--- a/tiger_audit_blue_ash_montgomery/reports/TIGER-Audit-Blue-Ash-Montgomery.xlsx
+++ b/tiger_audit_blue_ash_montgomery/reports/TIGER-Audit-Blue-Ash-Montgomery.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>Audit date (UTC): 2026-04-29T01:57:46+00:00</t>
+          <t>Audit date (UTC): 2026-04-29T02:09:45+00:00</t>
         </is>
       </c>
     </row>
@@ -2128,18 +2128,18 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Kugler Mill Road</t>
+          <t>Hosbrook Road</t>
         </is>
       </c>
       <c r="C16" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="D16" s="5" t="n">
-        <v>0</v>
+      <c r="D16" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>residential, tertiary, unclassified</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>East Columbia Avenue</t>
+          <t>Kugler Mill Road</t>
         </is>
       </c>
       <c r="C17" s="5" t="n">
@@ -2165,7 +2165,7 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>secondary</t>
+          <t>residential, tertiary, unclassified</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
@@ -2206,18 +2206,18 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Hosbrook Road</t>
+          <t>East Columbia Avenue</t>
         </is>
       </c>
       <c r="C19" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="D19" s="10" t="n">
-        <v>2</v>
+      <c r="D19" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>secondary</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
@@ -2258,7 +2258,7 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Camargo Road</t>
+          <t>Ibsen Avenue</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>secondary, tertiary</t>
+          <t>tertiary</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
@@ -2284,7 +2284,7 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Ibsen Avenue</t>
+          <t>Camargo Road</t>
         </is>
       </c>
       <c r="C22" s="5" t="n">
@@ -2295,7 +2295,7 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>tertiary</t>
+          <t>secondary, tertiary</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
@@ -2336,18 +2336,18 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>Fox Run Drive</t>
+          <t>Reed Hartman Highway</t>
         </is>
       </c>
       <c r="C24" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="D24" s="10" t="n">
-        <v>4</v>
+      <c r="D24" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>secondary</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
@@ -2362,18 +2362,18 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Reed Hartman Highway</t>
+          <t>Fox Run Drive</t>
         </is>
       </c>
       <c r="C25" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="D25" s="5" t="n">
-        <v>0</v>
+      <c r="D25" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>secondary</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
@@ -2388,18 +2388,18 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>Stewart Avenue</t>
+          <t>Hunters Creek Drive</t>
         </is>
       </c>
       <c r="C26" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="D26" s="5" t="n">
-        <v>0</v>
+      <c r="D26" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>residential, secondary, tertiary</t>
+          <t>residential, service</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Miami Road</t>
+          <t>Stewart Avenue</t>
         </is>
       </c>
       <c r="C27" s="5" t="n">
@@ -2425,7 +2425,7 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>secondary</t>
+          <t>residential, secondary, tertiary</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
@@ -2440,18 +2440,18 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>Hunters Creek Drive</t>
+          <t>Miami Road</t>
         </is>
       </c>
       <c r="C28" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="D28" s="10" t="n">
-        <v>2</v>
+      <c r="D28" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>residential, service</t>
+          <t>secondary</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
@@ -2466,7 +2466,7 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Dawson Road</t>
+          <t>Schenck Avenue</t>
         </is>
       </c>
       <c r="C29" s="5" t="n">
@@ -2477,7 +2477,7 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>tertiary</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
@@ -2492,7 +2492,7 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>Schenck Avenue</t>
+          <t>Alamo Avenue</t>
         </is>
       </c>
       <c r="C30" s="5" t="n">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>tertiary</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Eastwood Drive</t>
+          <t>Dawson Road</t>
         </is>
       </c>
       <c r="C31" s="5" t="n">
@@ -2529,7 +2529,7 @@
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>tertiary</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
@@ -2570,7 +2570,7 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Alamo Avenue</t>
+          <t>Eastwood Drive</t>
         </is>
       </c>
       <c r="C33" s="5" t="n">
@@ -2581,7 +2581,7 @@
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>tertiary</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
@@ -73002,12 +73002,14 @@
           <t>Springdale / Sharonville</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
-        <is>
-          <t>NOT STARTED</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr"/>
+      <c r="B3" s="12" t="inlineStr">
+        <is>
+          <t>AUDIT COMPLETE</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="n">
+        <v>1549</v>
+      </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
           <t>Springdale, Sharonville, Glendale, Evendale, Lincoln Heights</t>
@@ -73020,12 +73022,14 @@
           <t>Northgate / Mt. Healthy</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
-        <is>
-          <t>NOT STARTED</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr"/>
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>AUDIT COMPLETE</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>1664</v>
+      </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
           <t>Mt. Healthy, North College Hill, Finneytown, Northgate</t>
@@ -73038,12 +73042,14 @@
           <t>Forest Park / Pleasant Run</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
-        <is>
-          <t>NOT STARTED</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr"/>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>AUDIT COMPLETE</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>2066</v>
+      </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
           <t>Forest Park, Pleasant Run, Greenhills</t>
@@ -73247,7 +73253,7 @@
       </c>
       <c r="B3" s="15" t="inlineStr">
         <is>
-          <t>2026-04-29T01:57:46+00:00</t>
+          <t>2026-04-29T02:09:45+00:00</t>
         </is>
       </c>
     </row>

--- a/tiger_audit_blue_ash_montgomery/reports/TIGER-Audit-Blue-Ash-Montgomery.xlsx
+++ b/tiger_audit_blue_ash_montgomery/reports/TIGER-Audit-Blue-Ash-Montgomery.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>Audit date (UTC): 2026-04-29T02:09:45+00:00</t>
+          <t>Audit date (UTC): 2026-04-29T02:18:29+00:00</t>
         </is>
       </c>
     </row>
@@ -2128,18 +2128,18 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Hosbrook Road</t>
+          <t>Kugler Mill Road</t>
         </is>
       </c>
       <c r="C16" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="D16" s="10" t="n">
-        <v>2</v>
+      <c r="D16" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>residential, tertiary, unclassified</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
@@ -2154,18 +2154,18 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Kugler Mill Road</t>
+          <t>Hosbrook Road</t>
         </is>
       </c>
       <c r="C17" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="D17" s="5" t="n">
-        <v>0</v>
+      <c r="D17" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>residential, tertiary, unclassified</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
@@ -2336,18 +2336,18 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>Reed Hartman Highway</t>
+          <t>Fox Run Drive</t>
         </is>
       </c>
       <c r="C24" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="D24" s="5" t="n">
-        <v>0</v>
+      <c r="D24" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>secondary</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
@@ -2362,18 +2362,18 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Fox Run Drive</t>
+          <t>Reed Hartman Highway</t>
         </is>
       </c>
       <c r="C25" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="D25" s="10" t="n">
-        <v>4</v>
+      <c r="D25" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>secondary</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
@@ -2388,18 +2388,18 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>Hunters Creek Drive</t>
+          <t>Stewart Avenue</t>
         </is>
       </c>
       <c r="C26" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="D26" s="10" t="n">
-        <v>2</v>
+      <c r="D26" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>residential, service</t>
+          <t>residential, secondary, tertiary</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
@@ -2414,18 +2414,18 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Stewart Avenue</t>
+          <t>Hunters Creek Drive</t>
         </is>
       </c>
       <c r="C27" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="D27" s="5" t="n">
-        <v>0</v>
+      <c r="D27" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>residential, secondary, tertiary</t>
+          <t>residential, service</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
@@ -2466,7 +2466,7 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Schenck Avenue</t>
+          <t>Alamo Avenue</t>
         </is>
       </c>
       <c r="C29" s="5" t="n">
@@ -2477,7 +2477,7 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>tertiary</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
@@ -2492,7 +2492,7 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>Alamo Avenue</t>
+          <t>Laurel Avenue</t>
         </is>
       </c>
       <c r="C30" s="5" t="n">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>tertiary</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Dawson Road</t>
+          <t>Schenck Avenue</t>
         </is>
       </c>
       <c r="C31" s="5" t="n">
@@ -2529,7 +2529,7 @@
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>tertiary</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
@@ -2544,7 +2544,7 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>Commons Road</t>
+          <t>Dawson Road</t>
         </is>
       </c>
       <c r="C32" s="5" t="n">
@@ -2555,7 +2555,7 @@
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>tertiary</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
@@ -2570,7 +2570,7 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Eastwood Drive</t>
+          <t>Commons Road</t>
         </is>
       </c>
       <c r="C33" s="5" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>Laurel Avenue</t>
+          <t>Eastwood Drive</t>
         </is>
       </c>
       <c r="C34" s="5" t="n">
@@ -73253,7 +73253,7 @@
       </c>
       <c r="B3" s="15" t="inlineStr">
         <is>
-          <t>2026-04-29T02:09:45+00:00</t>
+          <t>2026-04-29T02:18:29+00:00</t>
         </is>
       </c>
     </row>

--- a/tiger_audit_blue_ash_montgomery/reports/TIGER-Audit-Blue-Ash-Montgomery.xlsx
+++ b/tiger_audit_blue_ash_montgomery/reports/TIGER-Audit-Blue-Ash-Montgomery.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>Audit date (UTC): 2026-04-29T02:18:29+00:00</t>
+          <t>Audit date (UTC): 2026-04-29T02:33:55+00:00</t>
         </is>
       </c>
     </row>
@@ -2154,18 +2154,18 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Hosbrook Road</t>
+          <t>East Columbia Avenue</t>
         </is>
       </c>
       <c r="C17" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="D17" s="10" t="n">
-        <v>2</v>
+      <c r="D17" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>secondary</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
@@ -2206,18 +2206,18 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>East Columbia Avenue</t>
+          <t>Hosbrook Road</t>
         </is>
       </c>
       <c r="C19" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="D19" s="5" t="n">
-        <v>0</v>
+      <c r="D19" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>secondary</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
@@ -2310,18 +2310,18 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Malsbary Road</t>
+          <t>Reed Hartman Highway</t>
         </is>
       </c>
       <c r="C23" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="D23" s="10" t="n">
-        <v>4</v>
+      <c r="D23" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>unclassified</t>
+          <t>secondary</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
@@ -2336,7 +2336,7 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>Fox Run Drive</t>
+          <t>Malsbary Road</t>
         </is>
       </c>
       <c r="C24" s="5" t="n">
@@ -2347,7 +2347,7 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>unclassified</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
@@ -2362,18 +2362,18 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Reed Hartman Highway</t>
+          <t>Fox Run Drive</t>
         </is>
       </c>
       <c r="C25" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="D25" s="5" t="n">
-        <v>0</v>
+      <c r="D25" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>secondary</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
@@ -2466,7 +2466,7 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Alamo Avenue</t>
+          <t>Eastwood Drive</t>
         </is>
       </c>
       <c r="C29" s="5" t="n">
@@ -2477,7 +2477,7 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>tertiary</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
@@ -2492,7 +2492,7 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>Laurel Avenue</t>
+          <t>Alamo Avenue</t>
         </is>
       </c>
       <c r="C30" s="5" t="n">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>tertiary</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
@@ -2544,7 +2544,7 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>Dawson Road</t>
+          <t>Laurel Avenue</t>
         </is>
       </c>
       <c r="C32" s="5" t="n">
@@ -2555,7 +2555,7 @@
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>tertiary</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>Eastwood Drive</t>
+          <t>Dawson Road</t>
         </is>
       </c>
       <c r="C34" s="5" t="n">
@@ -2607,7 +2607,7 @@
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>tertiary</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
@@ -73253,7 +73253,7 @@
       </c>
       <c r="B3" s="15" t="inlineStr">
         <is>
-          <t>2026-04-29T02:18:29+00:00</t>
+          <t>2026-04-29T02:33:55+00:00</t>
         </is>
       </c>
     </row>

--- a/tiger_audit_blue_ash_montgomery/reports/TIGER-Audit-Blue-Ash-Montgomery.xlsx
+++ b/tiger_audit_blue_ash_montgomery/reports/TIGER-Audit-Blue-Ash-Montgomery.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>Audit date (UTC): 2026-04-29T02:33:55+00:00</t>
+          <t>Audit date (UTC): 2026-04-29T02:42:02+00:00</t>
         </is>
       </c>
     </row>
@@ -2128,7 +2128,7 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Kugler Mill Road</t>
+          <t>Woodford Road</t>
         </is>
       </c>
       <c r="C16" s="5" t="n">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>residential, tertiary, unclassified</t>
+          <t>tertiary</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
@@ -2180,18 +2180,18 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Woodford Road</t>
+          <t>Hosbrook Road</t>
         </is>
       </c>
       <c r="C18" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="D18" s="5" t="n">
-        <v>0</v>
+      <c r="D18" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>tertiary</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
@@ -2206,18 +2206,18 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Hosbrook Road</t>
+          <t>Kugler Mill Road</t>
         </is>
       </c>
       <c r="C19" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="D19" s="10" t="n">
-        <v>2</v>
+      <c r="D19" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>residential, tertiary, unclassified</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
@@ -2258,7 +2258,7 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Ibsen Avenue</t>
+          <t>Camargo Road</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>tertiary</t>
+          <t>secondary, tertiary</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
@@ -2284,7 +2284,7 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Camargo Road</t>
+          <t>Ibsen Avenue</t>
         </is>
       </c>
       <c r="C22" s="5" t="n">
@@ -2295,7 +2295,7 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>secondary, tertiary</t>
+          <t>tertiary</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
@@ -2388,18 +2388,18 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>Stewart Avenue</t>
+          <t>Hunters Creek Drive</t>
         </is>
       </c>
       <c r="C26" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="D26" s="5" t="n">
-        <v>0</v>
+      <c r="D26" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>residential, secondary, tertiary</t>
+          <t>residential, service</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
@@ -2414,18 +2414,18 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Hunters Creek Drive</t>
+          <t>Stewart Avenue</t>
         </is>
       </c>
       <c r="C27" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="D27" s="10" t="n">
-        <v>2</v>
+      <c r="D27" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>residential, service</t>
+          <t>residential, secondary, tertiary</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
@@ -2492,7 +2492,7 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>Alamo Avenue</t>
+          <t>Schenck Avenue</t>
         </is>
       </c>
       <c r="C30" s="5" t="n">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>tertiary</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Schenck Avenue</t>
+          <t>Alamo Avenue</t>
         </is>
       </c>
       <c r="C31" s="5" t="n">
@@ -2529,7 +2529,7 @@
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>tertiary</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
@@ -2544,7 +2544,7 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>Laurel Avenue</t>
+          <t>Commons Road</t>
         </is>
       </c>
       <c r="C32" s="5" t="n">
@@ -2570,7 +2570,7 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Commons Road</t>
+          <t>Dawson Road</t>
         </is>
       </c>
       <c r="C33" s="5" t="n">
@@ -2581,7 +2581,7 @@
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>tertiary</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>Dawson Road</t>
+          <t>Laurel Avenue</t>
         </is>
       </c>
       <c r="C34" s="5" t="n">
@@ -2607,7 +2607,7 @@
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>tertiary</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
@@ -73253,7 +73253,7 @@
       </c>
       <c r="B3" s="15" t="inlineStr">
         <is>
-          <t>2026-04-29T02:33:55+00:00</t>
+          <t>2026-04-29T02:42:02+00:00</t>
         </is>
       </c>
     </row>

--- a/tiger_audit_blue_ash_montgomery/reports/TIGER-Audit-Blue-Ash-Montgomery.xlsx
+++ b/tiger_audit_blue_ash_montgomery/reports/TIGER-Audit-Blue-Ash-Montgomery.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>Audit date (UTC): 2026-04-29T02:42:02+00:00</t>
+          <t>Audit date (UTC): 2026-04-29T02:49:14+00:00</t>
         </is>
       </c>
     </row>
@@ -2128,7 +2128,7 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Woodford Road</t>
+          <t>East Columbia Avenue</t>
         </is>
       </c>
       <c r="C16" s="5" t="n">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>tertiary</t>
+          <t>secondary</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
@@ -2154,18 +2154,18 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>East Columbia Avenue</t>
+          <t>Hosbrook Road</t>
         </is>
       </c>
       <c r="C17" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="D17" s="5" t="n">
-        <v>0</v>
+      <c r="D17" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>secondary</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
@@ -2180,18 +2180,18 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Hosbrook Road</t>
+          <t>Kugler Mill Road</t>
         </is>
       </c>
       <c r="C18" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="D18" s="10" t="n">
-        <v>2</v>
+      <c r="D18" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>residential, tertiary, unclassified</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Kugler Mill Road</t>
+          <t>Woodford Road</t>
         </is>
       </c>
       <c r="C19" s="5" t="n">
@@ -2217,7 +2217,7 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>residential, tertiary, unclassified</t>
+          <t>tertiary</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
@@ -2336,7 +2336,7 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>Malsbary Road</t>
+          <t>Fox Run Drive</t>
         </is>
       </c>
       <c r="C24" s="5" t="n">
@@ -2347,7 +2347,7 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>unclassified</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
@@ -2362,7 +2362,7 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Fox Run Drive</t>
+          <t>Malsbary Road</t>
         </is>
       </c>
       <c r="C25" s="5" t="n">
@@ -2373,7 +2373,7 @@
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>unclassified</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
@@ -2388,18 +2388,18 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>Hunters Creek Drive</t>
+          <t>Miami Road</t>
         </is>
       </c>
       <c r="C26" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="D26" s="10" t="n">
-        <v>2</v>
+      <c r="D26" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>residential, service</t>
+          <t>secondary</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
@@ -2440,18 +2440,18 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>Miami Road</t>
+          <t>Hunters Creek Drive</t>
         </is>
       </c>
       <c r="C28" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="D28" s="5" t="n">
-        <v>0</v>
+      <c r="D28" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>secondary</t>
+          <t>residential, service</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Alamo Avenue</t>
+          <t>Commons Road</t>
         </is>
       </c>
       <c r="C31" s="5" t="n">
@@ -2529,7 +2529,7 @@
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>tertiary</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
@@ -2544,7 +2544,7 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>Commons Road</t>
+          <t>Alamo Avenue</t>
         </is>
       </c>
       <c r="C32" s="5" t="n">
@@ -2555,7 +2555,7 @@
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>tertiary</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
@@ -73253,7 +73253,7 @@
       </c>
       <c r="B3" s="15" t="inlineStr">
         <is>
-          <t>2026-04-29T02:42:02+00:00</t>
+          <t>2026-04-29T02:49:14+00:00</t>
         </is>
       </c>
     </row>

--- a/tiger_audit_blue_ash_montgomery/reports/TIGER-Audit-Blue-Ash-Montgomery.xlsx
+++ b/tiger_audit_blue_ash_montgomery/reports/TIGER-Audit-Blue-Ash-Montgomery.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>Audit date (UTC): 2026-04-29T02:49:14+00:00</t>
+          <t>Audit date (UTC): 2026-04-29T13:07:54+00:00</t>
         </is>
       </c>
     </row>
@@ -2128,7 +2128,7 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>East Columbia Avenue</t>
+          <t>Woodford Road</t>
         </is>
       </c>
       <c r="C16" s="5" t="n">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>secondary</t>
+          <t>tertiary</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Woodford Road</t>
+          <t>East Columbia Avenue</t>
         </is>
       </c>
       <c r="C19" s="5" t="n">
@@ -2217,7 +2217,7 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>tertiary</t>
+          <t>secondary</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
@@ -2310,18 +2310,18 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Reed Hartman Highway</t>
+          <t>Malsbary Road</t>
         </is>
       </c>
       <c r="C23" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="D23" s="5" t="n">
-        <v>0</v>
+      <c r="D23" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>secondary</t>
+          <t>unclassified</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
@@ -2362,18 +2362,18 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Malsbary Road</t>
+          <t>Reed Hartman Highway</t>
         </is>
       </c>
       <c r="C25" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="D25" s="10" t="n">
-        <v>4</v>
+      <c r="D25" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>unclassified</t>
+          <t>secondary</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
@@ -2388,7 +2388,7 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>Miami Road</t>
+          <t>Stewart Avenue</t>
         </is>
       </c>
       <c r="C26" s="5" t="n">
@@ -2399,7 +2399,7 @@
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>secondary</t>
+          <t>residential, secondary, tertiary</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Stewart Avenue</t>
+          <t>Miami Road</t>
         </is>
       </c>
       <c r="C27" s="5" t="n">
@@ -2425,7 +2425,7 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>residential, secondary, tertiary</t>
+          <t>secondary</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
@@ -2466,7 +2466,7 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Eastwood Drive</t>
+          <t>Alamo Avenue</t>
         </is>
       </c>
       <c r="C29" s="5" t="n">
@@ -2477,7 +2477,7 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>tertiary</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
@@ -2492,7 +2492,7 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>Schenck Avenue</t>
+          <t>Dawson Road</t>
         </is>
       </c>
       <c r="C30" s="5" t="n">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>tertiary</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Commons Road</t>
+          <t>Eastwood Drive</t>
         </is>
       </c>
       <c r="C31" s="5" t="n">
@@ -2544,7 +2544,7 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>Alamo Avenue</t>
+          <t>Laurel Avenue</t>
         </is>
       </c>
       <c r="C32" s="5" t="n">
@@ -2555,7 +2555,7 @@
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>tertiary</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
@@ -2570,7 +2570,7 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Dawson Road</t>
+          <t>Commons Road</t>
         </is>
       </c>
       <c r="C33" s="5" t="n">
@@ -2581,7 +2581,7 @@
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>tertiary</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>Laurel Avenue</t>
+          <t>Schenck Avenue</t>
         </is>
       </c>
       <c r="C34" s="5" t="n">
@@ -73253,7 +73253,7 @@
       </c>
       <c r="B3" s="15" t="inlineStr">
         <is>
-          <t>2026-04-29T02:49:14+00:00</t>
+          <t>2026-04-29T13:07:54+00:00</t>
         </is>
       </c>
     </row>

--- a/tiger_audit_blue_ash_montgomery/reports/TIGER-Audit-Blue-Ash-Montgomery.xlsx
+++ b/tiger_audit_blue_ash_montgomery/reports/TIGER-Audit-Blue-Ash-Montgomery.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>Audit date (UTC): 2026-04-29T13:07:54+00:00</t>
+          <t>Audit date (UTC): 2026-04-30T17:05:33+00:00</t>
         </is>
       </c>
     </row>
@@ -2154,18 +2154,18 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Hosbrook Road</t>
+          <t>East Columbia Avenue</t>
         </is>
       </c>
       <c r="C17" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="D17" s="10" t="n">
-        <v>2</v>
+      <c r="D17" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>secondary</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
@@ -2206,18 +2206,18 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>East Columbia Avenue</t>
+          <t>Hosbrook Road</t>
         </is>
       </c>
       <c r="C19" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="D19" s="5" t="n">
-        <v>0</v>
+      <c r="D19" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>secondary</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
@@ -2310,18 +2310,18 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Malsbary Road</t>
+          <t>Reed Hartman Highway</t>
         </is>
       </c>
       <c r="C23" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="D23" s="10" t="n">
-        <v>4</v>
+      <c r="D23" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>unclassified</t>
+          <t>secondary</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
@@ -2362,18 +2362,18 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Reed Hartman Highway</t>
+          <t>Malsbary Road</t>
         </is>
       </c>
       <c r="C25" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="D25" s="5" t="n">
-        <v>0</v>
+      <c r="D25" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>secondary</t>
+          <t>unclassified</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
@@ -2388,18 +2388,18 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>Stewart Avenue</t>
+          <t>Hunters Creek Drive</t>
         </is>
       </c>
       <c r="C26" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="D26" s="5" t="n">
-        <v>0</v>
+      <c r="D26" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>residential, secondary, tertiary</t>
+          <t>residential, service</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Miami Road</t>
+          <t>Stewart Avenue</t>
         </is>
       </c>
       <c r="C27" s="5" t="n">
@@ -2425,7 +2425,7 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>secondary</t>
+          <t>residential, secondary, tertiary</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
@@ -2440,18 +2440,18 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>Hunters Creek Drive</t>
+          <t>Miami Road</t>
         </is>
       </c>
       <c r="C28" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="D28" s="10" t="n">
-        <v>2</v>
+      <c r="D28" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>residential, service</t>
+          <t>secondary</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
@@ -2466,7 +2466,7 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Alamo Avenue</t>
+          <t>Schenck Avenue</t>
         </is>
       </c>
       <c r="C29" s="5" t="n">
@@ -2477,7 +2477,7 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>tertiary</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
@@ -2492,7 +2492,7 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>Dawson Road</t>
+          <t>Laurel Avenue</t>
         </is>
       </c>
       <c r="C30" s="5" t="n">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>tertiary</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Eastwood Drive</t>
+          <t>Alamo Avenue</t>
         </is>
       </c>
       <c r="C31" s="5" t="n">
@@ -2529,7 +2529,7 @@
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>tertiary</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
@@ -2544,7 +2544,7 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>Laurel Avenue</t>
+          <t>Eastwood Drive</t>
         </is>
       </c>
       <c r="C32" s="5" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>Schenck Avenue</t>
+          <t>Dawson Road</t>
         </is>
       </c>
       <c r="C34" s="5" t="n">
@@ -2607,7 +2607,7 @@
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>tertiary</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
@@ -73253,7 +73253,7 @@
       </c>
       <c r="B3" s="15" t="inlineStr">
         <is>
-          <t>2026-04-29T13:07:54+00:00</t>
+          <t>2026-04-30T17:05:33+00:00</t>
         </is>
       </c>
     </row>
